--- a/excel/Batch_01_Leads_Tracker.xlsx
+++ b/excel/Batch_01_Leads_Tracker.xlsx
@@ -530,10 +530,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -604,10 +604,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -755,10 +755,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -830,10 +830,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -905,10 +905,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -983,10 +983,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1058,10 +1058,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -1131,10 +1131,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1205,10 +1205,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1281,10 +1281,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1354,10 +1354,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1428,10 +1428,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1502,10 +1502,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1577,10 +1577,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1650,10 +1650,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O17" t="str">
         <v/>

--- a/excel/Batch_01_Leads_Tracker.xlsx
+++ b/excel/Batch_01_Leads_Tracker.xlsx
@@ -1723,10 +1723,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1797,10 +1797,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1873,10 +1873,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1948,10 +1948,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -2022,10 +2022,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M22" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -2098,10 +2098,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M23" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -2172,10 +2172,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M24" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -2245,10 +2245,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M25" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -2319,10 +2319,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="M26" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>2026-09-07</v>
       </c>
       <c r="O26" t="str">
         <v/>

--- a/excel/Batch_01_Leads_Tracker.xlsx
+++ b/excel/Batch_01_Leads_Tracker.xlsx
@@ -398,23 +398,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:R26"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="52.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="52.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="36.83203125" customWidth="1"/>
+    <col min="7" max="7" width="52.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="52.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="36.83203125" customWidth="1"/>
+    <col min="15" max="15" width="52.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="32.83203125" customWidth="1"/>
+    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,33 +439,42 @@
         <v>Social Links</v>
       </c>
       <c r="F1" t="str">
+        <v>1st Email Subject</v>
+      </c>
+      <c r="G1" t="str">
         <v>1st Email</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Dates</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
+        <v>Follow Up 1 Subject</v>
+      </c>
+      <c r="K1" t="str">
         <v>Follow Up 1</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>Status</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Dates</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>Follow Up 2 Subject</v>
+      </c>
+      <c r="O1" t="str">
         <v>Follow Up 2</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Status</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Dates</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Lead Status</v>
       </c>
     </row>
@@ -482,7 +496,10 @@
 FMB
 Source page: https://www.greengroupconstruction.co.uk/</v>
       </c>
-      <c r="F2" t="str" xml:space="preserve">
+      <c r="F2" t="str">
+        <v>Website redesign idea for Green Group Construction</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Green Group Construction team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your loft conversions, extensions and refurbishments are clear business strengths. However, I noticed that the enquiry form shows a server error, the site still carries a 2015-era structure, and key trust points such as your guarantee and project experience are not easy to notice quickly. That can make potential customers hesitate or leave before contacting you.
@@ -493,13 +510,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G2" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H2" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I2" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Following up - Website redesign idea for Green Group Construction</v>
+      </c>
+      <c r="K2" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Green Group Construction team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the enquiry form shows a server error, the site still carries a 2015-era structure, and key trust points such as your guarantee and project experience are not easy to notice quickly. A cleaner homepage could help visitors understand your loft conversions, extensions and refurbishments faster and make it easier for them to enquire.
@@ -511,13 +531,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J2" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L2" t="str" xml:space="preserve">
+      <c r="L2" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Final follow-up - Website redesign idea for Green Group Construction</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Green Group Construction team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -529,13 +552,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M2" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q2" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O2" t="str">
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -556,7 +579,10 @@
         <v xml:space="preserve">WhatsApp: https://wa.me/447733403079
 Contact page: https://www.czconstruction.co.uk/contact--us.html</v>
       </c>
-      <c r="F3" t="str" xml:space="preserve">
+      <c r="F3" t="str">
+        <v>Website redesign idea for CZ Construction</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Constantine,
 I was looking through the CZ Construction website and liked the personal approach you take to managing projects from planning through completion.
 The current website communicates that experience, but its 2015-era layout, duplicated navigation, limited project presentation and enquiry-form problem make it harder for prospective clients to see the quality of your work and take the next step.
@@ -567,13 +593,16 @@
 Kind regards,
 Khaled Saifullah</v>
       </c>
-      <c r="G3" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H3" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I3" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Following up - Website redesign idea for CZ Construction</v>
+      </c>
+      <c r="K3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CZ Construction team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site has a dated 2015 layout, duplicated navigation, an enquiry-form error and limited project presentation. A cleaner homepage could help visitors understand your extensions, bathrooms, carpentry, plumbing and project management faster and make it easier for them to enquire.
@@ -585,13 +614,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J3" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L3" t="str" xml:space="preserve">
+      <c r="L3" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Final follow-up - Website redesign idea for CZ Construction</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CZ Construction team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -603,13 +635,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M3" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q3" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O3" t="str">
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
@@ -631,7 +663,10 @@
 Checkatrade: https://www.checkatrade.com/trades/yourchoicelocksandglazing
 Contact page: https://yourchoicelocksmiths.co.uk/your_choice_locksmiths_service_contact_us</v>
       </c>
-      <c r="F4" t="str" xml:space="preserve">
+      <c r="F4" t="str">
+        <v>Website redesign idea for Your Choice Locksmiths</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Your Choice Locksmiths team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your locksmith, glazing and boarding-up services are clear business strengths. However, I noticed that the site has crowded navigation, repeated content and long area lists that distract from the urgent call action. That can make potential customers hesitate or leave before contacting you.
@@ -642,13 +677,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G4" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H4" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I4" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Following up - Website redesign idea for Your Choice Locksmiths</v>
+      </c>
+      <c r="K4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Your Choice Locksmiths team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site has crowded navigation, repeated content and long area lists that distract from the urgent call action. A cleaner homepage could help visitors understand your locksmith, glazing and boarding-up services faster and make it easier for them to enquire.
@@ -660,13 +698,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>Replied</v>
       </c>
-      <c r="K4" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L4" t="str" xml:space="preserve">
+      <c r="M4" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Final follow-up - Website redesign idea for Your Choice Locksmiths</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Your Choice Locksmiths team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -678,14 +719,14 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M4" t="str">
+      <c r="P4" t="str">
         <v>Draft</v>
       </c>
-      <c r="N4" t="str">
+      <c r="Q4" t="str">
         <v/>
       </c>
-      <c r="O4" t="str">
-        <v>Closed</v>
+      <c r="R4" t="str">
+        <v>Lost</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -707,7 +748,10 @@
 Facebook
 Checkatrade</v>
       </c>
-      <c r="F5" t="str" xml:space="preserve">
+      <c r="F5" t="str">
+        <v>Website redesign idea for BL Painting &amp; Decorating</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi BL Painting &amp; Decorating team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your painting, decorating and Italian specialist finishes are clear business strengths. However, I noticed that the contact page has a visible typo, the site still shows a 2015 footer, and the portfolio/trust proof could be presented much more strongly. That can make potential customers hesitate or leave before contacting you.
@@ -718,13 +762,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G5" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H5" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I5" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Following up - Website redesign idea for BL Painting &amp; Decorating</v>
+      </c>
+      <c r="K5" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi BL Painting &amp; Decorating team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the contact page has a visible typo, the site still shows a 2015 footer, and the portfolio/trust proof could be presented much more strongly. A cleaner homepage could help visitors understand your painting, decorating and Italian specialist finishes faster and make it easier for them to enquire.
@@ -736,13 +783,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J5" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K5" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L5" t="str" xml:space="preserve">
+      <c r="L5" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M5" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Final follow-up - Website redesign idea for BL Painting &amp; Decorating</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi BL Painting &amp; Decorating team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -754,13 +804,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M5" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q5" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O5" t="str">
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
@@ -782,7 +832,10 @@
 Facebook: https://www.facebook.com/100069001283816/
 Profile page: https://cvcdecoratorsltd.com/our-work/</v>
       </c>
-      <c r="F6" t="str" xml:space="preserve">
+      <c r="F6" t="str">
+        <v>Website redesign idea for CVC Decorators</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CVC Decorators team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your decorating, renovations, restoration and commercial refurbishment are clear business strengths. However, I noticed that the homepage repeats footer/contact content, has an older presentation, and does not show project storytelling as clearly as it could. That can make potential customers hesitate or leave before contacting you.
@@ -793,13 +846,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G6" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H6" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I6" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I6" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Following up - Website redesign idea for CVC Decorators</v>
+      </c>
+      <c r="K6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CVC Decorators team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the homepage repeats footer/contact content, has an older presentation, and does not show project storytelling as clearly as it could. A cleaner homepage could help visitors understand your decorating, renovations, restoration and commercial refurbishment faster and make it easier for them to enquire.
@@ -811,13 +867,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J6" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K6" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L6" t="str" xml:space="preserve">
+      <c r="L6" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Final follow-up - Website redesign idea for CVC Decorators</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CVC Decorators team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -829,13 +888,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M6" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q6" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O6" t="str">
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
@@ -857,7 +916,10 @@
 Instagram: https://www.instagram.com/brightmasterlondon/
 Contact page: https://brightmaster.co.uk/contact/</v>
       </c>
-      <c r="F7" t="str" xml:space="preserve">
+      <c r="F7" t="str">
+        <v>Website redesign idea for BrightMaster</v>
+      </c>
+      <c r="G7" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi BrightMaster team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your renovations, loft conversions and house extensions are clear business strengths. However, I noticed that the site still shows a 2015 footer, relies on an older slider-style layout, and hides strong testimonials lower down the page. That can make potential customers hesitate or leave before contacting you.
@@ -868,13 +930,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G7" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H7" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I7" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Following up - Website redesign idea for BrightMaster</v>
+      </c>
+      <c r="K7" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi BrightMaster team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site still shows a 2015 footer, relies on an older slider-style layout, and hides strong testimonials lower down the page. A cleaner homepage could help visitors understand your renovations, loft conversions and house extensions faster and make it easier for them to enquire.
@@ -886,13 +951,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J7" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K7" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L7" t="str" xml:space="preserve">
+      <c r="L7" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M7" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Final follow-up - Website redesign idea for BrightMaster</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi BrightMaster team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -904,13 +972,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M7" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q7" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O7" t="str">
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
@@ -935,7 +1003,10 @@
 MyBuilder: https://www.mybuilder.com/profile/agimlleshi
 Companies House: https://find-and-update.company-information.service.gov.uk/company/05445758</v>
       </c>
-      <c r="F8" t="str" xml:space="preserve">
+      <c r="F8" t="str">
+        <v>Website redesign idea for A&amp;B London Construction Services Ltd</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi A&amp;B London Construction Services Ltd team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your new builds, extensions, refurbishments and general building work are clear business strengths. However, I noticed that the homepage uses a 2014 structure with visible spelling and spacing issues, which can weaken trust for higher-value building enquiries. That can make potential customers hesitate or leave before contacting you.
@@ -946,13 +1017,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G8" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H8" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I8" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I8" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Following up - Website redesign idea for A&amp;B London Construction Services Ltd</v>
+      </c>
+      <c r="K8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi A&amp;B London Construction Services Ltd team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the homepage uses a 2014 structure with visible spelling and spacing issues, which can weaken trust for higher-value building enquiries. A cleaner homepage could help visitors understand your new builds, extensions, refurbishments and general building work faster and make it easier for them to enquire.
@@ -964,13 +1038,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J8" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K8" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="L8" t="str" xml:space="preserve">
+      <c r="L8" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M8" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Final follow-up - Website redesign idea for A&amp;B London Construction Services Ltd</v>
+      </c>
+      <c r="O8" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi A&amp;B London Construction Services Ltd team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -982,13 +1059,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M8" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q8" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O8" t="str">
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
@@ -1010,7 +1087,10 @@
 find-and-update.company-information.service.gov.uk: https://find-and-update.company-information.service.gov.uk/company/07221127/officers
 Directory: https://directory.getwestlondon.co.uk/company/8099bd4fb98a3cce337ad83f7205aeda</v>
       </c>
-      <c r="F9" t="str" xml:space="preserve">
+      <c r="F9" t="str">
+        <v>Website redesign idea for Dray Decorators</v>
+      </c>
+      <c r="G9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Dray Decorators team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your painting and decorating services are clear business strengths. However, I noticed that the website has an older layout, limited trust structure and contact details that are not presented in a modern conversion-focused way. That can make potential customers hesitate or leave before contacting you.
@@ -1021,13 +1101,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G9" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H9" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I9" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I9" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Following up - Website redesign idea for Dray Decorators</v>
+      </c>
+      <c r="K9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Dray Decorators team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the website has an older layout, limited trust structure and contact details that are not presented in a modern conversion-focused way. A cleaner homepage could help visitors understand your painting and decorating services faster and make it easier for them to enquire.
@@ -1039,13 +1122,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J9" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M9" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L9" t="str" xml:space="preserve">
+      <c r="N9" t="str">
+        <v>Final follow-up - Website redesign idea for Dray Decorators</v>
+      </c>
+      <c r="O9" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Dray Decorators team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1057,13 +1143,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M9" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q9" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O9" t="str">
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
@@ -1083,7 +1169,10 @@
       <c r="E10" t="str">
         <v>Houzz: https://www.houzz.co.uk/professionals/upholsterers/antonio-upholstery-pfvwgb-pf~597356454</v>
       </c>
-      <c r="F10" t="str" xml:space="preserve">
+      <c r="F10" t="str">
+        <v>Website redesign idea for Antonio Upholstery</v>
+      </c>
+      <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Antonio Upholstery team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your upholstery, restoration, curtains, blinds and bespoke furniture work are clear business strengths. However, I noticed that the site still shows a 2014 footer, has some rough wording, and could make craftsmanship, gallery proof and booking a home visit clearer. That can make potential customers hesitate or leave before contacting you.
@@ -1094,13 +1183,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G10" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H10" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I10" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I10" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Following up - Website redesign idea for Antonio Upholstery</v>
+      </c>
+      <c r="K10" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Antonio Upholstery team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site still shows a 2014 footer, has some rough wording, and could make craftsmanship, gallery proof and booking a home visit clearer. A cleaner homepage could help visitors understand your upholstery, restoration, curtains, blinds and bespoke furniture work faster and make it easier for them to enquire.
@@ -1112,13 +1204,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J10" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M10" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L10" t="str" xml:space="preserve">
+      <c r="N10" t="str">
+        <v>Final follow-up - Website redesign idea for Antonio Upholstery</v>
+      </c>
+      <c r="O10" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Antonio Upholstery team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1130,13 +1225,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M10" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q10" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O10" t="str">
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
@@ -1157,7 +1252,10 @@
         <v xml:space="preserve">WhatsApp: https://wa.me/447956322534
 Website about page: https://www.ctscleaningsolutionsltd.co.uk/about</v>
       </c>
-      <c r="F11" t="str" xml:space="preserve">
+      <c r="F11" t="str">
+        <v>Website redesign idea for CTS Cleaning Solutions</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CTS Cleaning Solutions team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your commercial, domestic and specialist cleaning services are clear business strengths. However, I noticed that the site still contains placeholder text such as 'Street Address' and 'Your Custom Text Here', which can reduce confidence before someone calls. That can make potential customers hesitate or leave before contacting you.
@@ -1168,13 +1266,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G11" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H11" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I11" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Following up - Website redesign idea for CTS Cleaning Solutions</v>
+      </c>
+      <c r="K11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CTS Cleaning Solutions team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site still contains placeholder text such as 'Street Address' and 'Your Custom Text Here', which can reduce confidence before someone calls. A cleaner homepage could help visitors understand your commercial, domestic and specialist cleaning services faster and make it easier for them to enquire.
@@ -1186,13 +1287,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J11" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M11" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L11" t="str" xml:space="preserve">
+      <c r="N11" t="str">
+        <v>Final follow-up - Website redesign idea for CTS Cleaning Solutions</v>
+      </c>
+      <c r="O11" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi CTS Cleaning Solutions team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1204,13 +1308,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M11" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q11" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O11" t="str">
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
@@ -1233,7 +1337,10 @@
 Companies House: https://find-and-update.company-information.service.gov.uk/company/03588369
 Website social page: https://www.rdbull.com/fbandtwit.html</v>
       </c>
-      <c r="F12" t="str" xml:space="preserve">
+      <c r="F12" t="str">
+        <v>Website redesign idea for R D Bull &amp; Sons</v>
+      </c>
+      <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi R D Bull &amp; Sons team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your building and property maintenance contracting are clear business strengths. However, I noticed that the homepage still relies on Flash content, older layout conventions and dense side navigation. That can make potential customers hesitate or leave before contacting you.
@@ -1244,13 +1351,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G12" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H12" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I12" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Following up - Website redesign idea for R D Bull &amp; Sons</v>
+      </c>
+      <c r="K12" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi R D Bull &amp; Sons team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the homepage still relies on Flash content, older layout conventions and dense side navigation. A cleaner homepage could help visitors understand your building and property maintenance contracting faster and make it easier for them to enquire.
@@ -1262,13 +1372,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J12" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M12" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L12" t="str" xml:space="preserve">
+      <c r="N12" t="str">
+        <v>Final follow-up - Website redesign idea for R D Bull &amp; Sons</v>
+      </c>
+      <c r="O12" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi R D Bull &amp; Sons team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1280,13 +1393,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M12" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q12" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O12" t="str">
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
@@ -1306,7 +1419,10 @@
       <c r="E13" t="str">
         <v>LinkedIn: https://uk.linkedin.com/in/paul-creed-0362aa40</v>
       </c>
-      <c r="F13" t="str" xml:space="preserve">
+      <c r="F13" t="str">
+        <v>Website redesign idea for Paul Creed Building Services</v>
+      </c>
+      <c r="G13" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Paul Creed Building Services team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your general building services are clear business strengths. However, I noticed that the site appears very basic and could do more to show project proof, trust signals and a clear enquiry journey. That can make potential customers hesitate or leave before contacting you.
@@ -1317,13 +1433,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G13" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H13" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I13" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Following up - Website redesign idea for Paul Creed Building Services</v>
+      </c>
+      <c r="K13" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Paul Creed Building Services team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site appears very basic and could do more to show project proof, trust signals and a clear enquiry journey. A cleaner homepage could help visitors understand your general building services faster and make it easier for them to enquire.
@@ -1335,13 +1454,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J13" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M13" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L13" t="str" xml:space="preserve">
+      <c r="N13" t="str">
+        <v>Final follow-up - Website redesign idea for Paul Creed Building Services</v>
+      </c>
+      <c r="O13" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Paul Creed Building Services team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1353,13 +1475,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M13" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q13" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O13" t="str">
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
@@ -1380,7 +1502,10 @@
         <v xml:space="preserve">WhatsApp: https://wa.me/447543547986
 Website: https://freshtouchlondon.com/</v>
       </c>
-      <c r="F14" t="str" xml:space="preserve">
+      <c r="F14" t="str">
+        <v>Website redesign idea for Fresh Touch Dry Cleaners</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Fresh Touch Dry Cleaners team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your dry cleaning, tailoring, laundry and shoe repairs are clear business strengths. However, I noticed that the site has mixed messaging, duplicated outlet/contact sections and weak conversion structure around pickup, delivery and pricing. That can make potential customers hesitate or leave before contacting you.
@@ -1391,13 +1516,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G14" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H14" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I14" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Following up - Website redesign idea for Fresh Touch Dry Cleaners</v>
+      </c>
+      <c r="K14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Fresh Touch Dry Cleaners team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site has mixed messaging, duplicated outlet/contact sections and weak conversion structure around pickup, delivery and pricing. A cleaner homepage could help visitors understand your dry cleaning, tailoring, laundry and shoe repairs faster and make it easier for them to enquire.
@@ -1409,13 +1537,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J14" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M14" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L14" t="str" xml:space="preserve">
+      <c r="N14" t="str">
+        <v>Final follow-up - Website redesign idea for Fresh Touch Dry Cleaners</v>
+      </c>
+      <c r="O14" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Fresh Touch Dry Cleaners team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1427,13 +1558,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M14" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q14" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O14" t="str">
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
@@ -1454,7 +1585,10 @@
         <v xml:space="preserve">WhatsApp: https://wa.me/447977482544
 Contact page: https://www.delancies.com/Contact.html</v>
       </c>
-      <c r="F15" t="str" xml:space="preserve">
+      <c r="F15" t="str">
+        <v>Website redesign idea for deLancies Chartered Surveyors</v>
+      </c>
+      <c r="G15" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi deLancies Chartered Surveyors team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your chartered surveying, valuations and expert witness services are clear business strengths. However, I noticed that the site still carries a 2010 copyright and Flash requirement, which can feel dated for clients considering professional valuation or survey work. That can make potential customers hesitate or leave before contacting you.
@@ -1465,13 +1599,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G15" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H15" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I15" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Following up - Website redesign idea for deLancies Chartered Surveyors</v>
+      </c>
+      <c r="K15" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi deLancies Chartered Surveyors team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site still carries a 2010 copyright and Flash requirement, which can feel dated for clients considering professional valuation or survey work. A cleaner homepage could help visitors understand your chartered surveying, valuations and expert witness services faster and make it easier for them to enquire.
@@ -1483,13 +1620,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J15" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M15" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="L15" t="str" xml:space="preserve">
+      <c r="N15" t="str">
+        <v>Final follow-up - Website redesign idea for deLancies Chartered Surveyors</v>
+      </c>
+      <c r="O15" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi deLancies Chartered Surveyors team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1501,13 +1641,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M15" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q15" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O15" t="str">
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
@@ -1529,7 +1669,10 @@
 Yell: https://www.yell.com/biz/classic-upholstery-london-10079390/
 Website: https://www.classic-upholstery.co.uk/</v>
       </c>
-      <c r="F16" t="str" xml:space="preserve">
+      <c r="F16" t="str">
+        <v>Website redesign idea for Classic Upholstery</v>
+      </c>
+      <c r="G16" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Classic Upholstery team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your upholstery, re-upholstery and soft furnishings are clear business strengths. However, I noticed that the site has strong experience and gallery content, but the 2015 presentation and long text blocks make the craftsmanship harder to scan quickly. That can make potential customers hesitate or leave before contacting you.
@@ -1540,13 +1683,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G16" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H16" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I16" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Following up - Website redesign idea for Classic Upholstery</v>
+      </c>
+      <c r="K16" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Classic Upholstery team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site has strong experience and gallery content, but the 2015 presentation and long text blocks make the craftsmanship harder to scan quickly. A cleaner homepage could help visitors understand your upholstery, re-upholstery and soft furnishings faster and make it easier for them to enquire.
@@ -1558,13 +1704,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J16" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M16" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L16" t="str" xml:space="preserve">
+      <c r="N16" t="str">
+        <v>Final follow-up - Website redesign idea for Classic Upholstery</v>
+      </c>
+      <c r="O16" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Classic Upholstery team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1576,13 +1725,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M16" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q16" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O16" t="str">
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
@@ -1602,7 +1751,10 @@
       <c r="E17" t="str">
         <v>Yell: https://www.yell.com/biz/minerva-motors-ltd-london-349004/</v>
       </c>
-      <c r="F17" t="str" xml:space="preserve">
+      <c r="F17" t="str">
+        <v>Website redesign idea for Minerva Motors</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Minerva Motors team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your MOT, servicing, diagnostics and bodywork are clear business strengths. However, I noticed that the site times out intermittently and has an older 1986-2013 style presentation, which can cost trust for MOT, diagnostics and repair enquiries. That can make potential customers hesitate or leave before contacting you.
@@ -1613,13 +1765,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G17" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H17" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I17" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Following up - Website redesign idea for Minerva Motors</v>
+      </c>
+      <c r="K17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Minerva Motors team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site times out intermittently and has an older 1986-2013 style presentation, which can cost trust for MOT, diagnostics and repair enquiries. A cleaner homepage could help visitors understand your MOT, servicing, diagnostics and bodywork faster and make it easier for them to enquire.
@@ -1631,13 +1786,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J17" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M17" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L17" t="str" xml:space="preserve">
+      <c r="N17" t="str">
+        <v>Final follow-up - Website redesign idea for Minerva Motors</v>
+      </c>
+      <c r="O17" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Minerva Motors team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1649,13 +1807,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M17" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q17" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O17" t="str">
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
@@ -1675,7 +1833,10 @@
       <c r="E18" t="str">
         <v>Website: https://www.greenhighbury.com/</v>
       </c>
-      <c r="F18" t="str" xml:space="preserve">
+      <c r="F18" t="str">
+        <v>Website redesign idea for C&amp;A Dry Cleaners</v>
+      </c>
+      <c r="G18" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi C&amp;A Dry Cleaners team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your dry cleaning and garment care are clear business strengths. However, I noticed that the website is very old, has under-review content, and does not present services, reviews or directions in a modern mobile-friendly way. That can make potential customers hesitate or leave before contacting you.
@@ -1686,13 +1847,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G18" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H18" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I18" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Following up - Website redesign idea for C&amp;A Dry Cleaners</v>
+      </c>
+      <c r="K18" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi C&amp;A Dry Cleaners team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the website is very old, has under-review content, and does not present services, reviews or directions in a modern mobile-friendly way. A cleaner homepage could help visitors understand your dry cleaning and garment care faster and make it easier for them to enquire.
@@ -1704,13 +1868,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J18" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M18" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L18" t="str" xml:space="preserve">
+      <c r="N18" t="str">
+        <v>Final follow-up - Website redesign idea for C&amp;A Dry Cleaners</v>
+      </c>
+      <c r="O18" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi C&amp;A Dry Cleaners team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1722,13 +1889,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M18" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q18" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O18" t="str">
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
@@ -1749,7 +1916,10 @@
         <v xml:space="preserve">WhatsApp: https://wa.me/447850623490
 Contact page: https://www.lk-builders.co.uk/contact.html</v>
       </c>
-      <c r="F19" t="str" xml:space="preserve">
+      <c r="F19" t="str">
+        <v>Website redesign idea for LK Builders</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi LK Builders team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your extensions, conversions, plastering and building work are clear business strengths. However, I noticed that the website currently returns a bad gateway in preview, and the contact page style appears dated, creating a risk that project enquiries are lost. That can make potential customers hesitate or leave before contacting you.
@@ -1760,13 +1930,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G19" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H19" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I19" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Following up - Website redesign idea for LK Builders</v>
+      </c>
+      <c r="K19" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi LK Builders team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the website currently returns a bad gateway in preview, and the contact page style appears dated, creating a risk that project enquiries are lost. A cleaner homepage could help visitors understand your extensions, conversions, plastering and building work faster and make it easier for them to enquire.
@@ -1778,13 +1951,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J19" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M19" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L19" t="str" xml:space="preserve">
+      <c r="N19" t="str">
+        <v>Final follow-up - Website redesign idea for LK Builders</v>
+      </c>
+      <c r="O19" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi LK Builders team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1796,13 +1972,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M19" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q19" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O19" t="str">
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
@@ -1825,7 +2001,10 @@
 Ouch.ai: https://www.ouch.ai/dentists/practice/stratford-village-dental-practice
 Facebook</v>
       </c>
-      <c r="F20" t="str" xml:space="preserve">
+      <c r="F20" t="str">
+        <v>Website redesign idea for Stratford Village Dental Practice</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Stratford Village Dental Practice team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your general, cosmetic and preventive dentistry are clear business strengths. However, I noticed that the site still shows a Flash requirement, older navigation and an old visual structure despite being updated recently. That can make potential customers hesitate or leave before contacting you.
@@ -1836,13 +2015,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G20" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H20" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I20" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I20" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Following up - Website redesign idea for Stratford Village Dental Practice</v>
+      </c>
+      <c r="K20" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Stratford Village Dental Practice team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site still shows a Flash requirement, older navigation and an old visual structure despite being updated recently. A cleaner homepage could help visitors understand your general, cosmetic and preventive dentistry faster and make it easier for them to enquire.
@@ -1854,13 +2036,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J20" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M20" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L20" t="str" xml:space="preserve">
+      <c r="N20" t="str">
+        <v>Final follow-up - Website redesign idea for Stratford Village Dental Practice</v>
+      </c>
+      <c r="O20" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Stratford Village Dental Practice team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1872,13 +2057,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M20" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q20" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O20" t="str">
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
@@ -1900,7 +2085,10 @@
 Associated sites: https://www.1stquotewindscreens.co.uk/
 Website: https://www.1stquoteautoscreens.co.uk/</v>
       </c>
-      <c r="F21" t="str" xml:space="preserve">
+      <c r="F21" t="str">
+        <v>Website redesign idea for 1st Quote AutoScreens</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi 1st Quote AutoScreens team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your windscreen repair and vehicle glass replacement are clear business strengths. However, I noticed that the site uses Flash prompts, very dense SEO text and an old 2010-2011 footer, which can weaken trust for urgent vehicle glass enquiries. That can make potential customers hesitate or leave before contacting you.
@@ -1911,13 +2099,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G21" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H21" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I21" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Following up - Website redesign idea for 1st Quote AutoScreens</v>
+      </c>
+      <c r="K21" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi 1st Quote AutoScreens team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site uses Flash prompts, very dense SEO text and an old 2010-2011 footer, which can weaken trust for urgent vehicle glass enquiries. A cleaner homepage could help visitors understand your windscreen repair and vehicle glass replacement faster and make it easier for them to enquire.
@@ -1929,13 +2120,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J21" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M21" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L21" t="str" xml:space="preserve">
+      <c r="N21" t="str">
+        <v>Final follow-up - Website redesign idea for 1st Quote AutoScreens</v>
+      </c>
+      <c r="O21" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi 1st Quote AutoScreens team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -1947,13 +2141,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M21" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q21" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O21" t="str">
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
@@ -1974,7 +2168,10 @@
         <v xml:space="preserve">WhatsApp: https://wa.me/447307053653
 Contact page: https://iflushsolutions.com/contact</v>
       </c>
-      <c r="F22" t="str" xml:space="preserve">
+      <c r="F22" t="str">
+        <v>Website redesign idea for Iflush Solutions</v>
+      </c>
+      <c r="G22" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Iflush Solutions team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your power flushing and plumbing services are clear business strengths. However, I noticed that the site has very sparse homepage content and older contact presentation, so the guarantee and power-flushing services could be much clearer. That can make potential customers hesitate or leave before contacting you.
@@ -1985,13 +2182,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G22" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H22" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I22" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Following up - Website redesign idea for Iflush Solutions</v>
+      </c>
+      <c r="K22" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Iflush Solutions team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the site has very sparse homepage content and older contact presentation, so the guarantee and power-flushing services could be much clearer. A cleaner homepage could help visitors understand your power flushing and plumbing services faster and make it easier for them to enquire.
@@ -2003,13 +2203,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J22" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M22" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L22" t="str" xml:space="preserve">
+      <c r="N22" t="str">
+        <v>Final follow-up - Website redesign idea for Iflush Solutions</v>
+      </c>
+      <c r="O22" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Iflush Solutions team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -2021,13 +2224,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M22" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q22" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O22" t="str">
+      <c r="R22" t="str">
         <v/>
       </c>
     </row>
@@ -2050,7 +2253,10 @@
 BuilderMarket: https://www.buildermarket.co.uk/business/priory-building-supplies
 Contact page: https://www.priorybuildingsupplies.com/contact.html</v>
       </c>
-      <c r="F23" t="str" xml:space="preserve">
+      <c r="F23" t="str">
+        <v>Website redesign idea for Priory Building Supplies</v>
+      </c>
+      <c r="G23" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Priory Building Supplies team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your building materials, roofing materials, timber and local delivery are clear business strengths. However, I noticed that the homepage still asks for Flash and carries a 2013 presentation, which can make the business look less current than it is. That can make potential customers hesitate or leave before contacting you.
@@ -2061,13 +2267,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G23" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H23" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I23" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I23" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Following up - Website redesign idea for Priory Building Supplies</v>
+      </c>
+      <c r="K23" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Priory Building Supplies team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the homepage still asks for Flash and carries a 2013 presentation, which can make the business look less current than it is. A cleaner homepage could help visitors understand your building materials, roofing materials, timber and local delivery faster and make it easier for them to enquire.
@@ -2079,13 +2288,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J23" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M23" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L23" t="str" xml:space="preserve">
+      <c r="N23" t="str">
+        <v>Final follow-up - Website redesign idea for Priory Building Supplies</v>
+      </c>
+      <c r="O23" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Priory Building Supplies team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -2097,13 +2309,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M23" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q23" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O23" t="str">
+      <c r="R23" t="str">
         <v/>
       </c>
     </row>
@@ -2123,7 +2335,10 @@
       <c r="E24" t="str">
         <v>Contact page: https://bruceupholstery.co.uk/contact.php</v>
       </c>
-      <c r="F24" t="str" xml:space="preserve">
+      <c r="F24" t="str">
+        <v>Website redesign idea for Bruce Upholstery &amp; Furniture Rescue</v>
+      </c>
+      <c r="G24" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bruce Upholstery team,
 Your combination of upholstery, furniture restoration and French polishing deserves a website that lets the work speak for itself.
 While reviewing your site, I found that the gallery still asks visitors to use Flash. That creates a particular obstacle for potential customers who want to inspect your craftsmanship before trusting you with a treasured piece.
@@ -2135,13 +2350,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G24" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H24" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I24" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I24" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Following up - Website redesign idea for Bruce Upholstery &amp; Furniture Rescue</v>
+      </c>
+      <c r="K24" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bruce Upholstery &amp; Furniture Rescue team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the gallery still asks visitors to use Flash, which prevents people from easily seeing your craftsmanship before making an enquiry. A cleaner homepage could help visitors understand your upholstery, furniture restoration and French polishing faster and make it easier for them to enquire.
@@ -2153,13 +2371,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J24" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M24" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L24" t="str" xml:space="preserve">
+      <c r="N24" t="str">
+        <v>Final follow-up - Website redesign idea for Bruce Upholstery &amp; Furniture Rescue</v>
+      </c>
+      <c r="O24" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Bruce Upholstery &amp; Furniture Rescue team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -2171,13 +2392,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M24" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q24" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O24" t="str">
+      <c r="R24" t="str">
         <v/>
       </c>
     </row>
@@ -2197,7 +2418,10 @@
       <c r="E25" t="str">
         <v>Website project/contact links: https://www.ajainteriors.co.uk/</v>
       </c>
-      <c r="F25" t="str" xml:space="preserve">
+      <c r="F25" t="str">
+        <v>Website redesign idea for AJA Interiors</v>
+      </c>
+      <c r="G25" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi AJA Interiors team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your office fit-out and refurbishment are clear business strengths. However, I noticed that the website carries a 2011 footer and the project proof could be presented in a more modern way for office fit-out buyers. That can make potential customers hesitate or leave before contacting you.
@@ -2208,13 +2432,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G25" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H25" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I25" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I25" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Following up - Website redesign idea for AJA Interiors</v>
+      </c>
+      <c r="K25" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi AJA Interiors team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the website carries a 2011 footer and the project proof could be presented in a more modern way for office fit-out buyers. A cleaner homepage could help visitors understand your office fit-out and refurbishment faster and make it easier for them to enquire.
@@ -2226,13 +2453,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J25" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M25" t="str">
         <v>2026-09-03</v>
       </c>
-      <c r="L25" t="str" xml:space="preserve">
+      <c r="N25" t="str">
+        <v>Final follow-up - Website redesign idea for AJA Interiors</v>
+      </c>
+      <c r="O25" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi AJA Interiors team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -2244,13 +2474,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M25" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q25" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O25" t="str">
+      <c r="R25" t="str">
         <v/>
       </c>
     </row>
@@ -2271,7 +2501,10 @@
         <v xml:space="preserve">Contact page: https://www.ductien.co.uk/pages/contact.php
 Profile page: https://www.ductien.co.uk/pages/signup.php</v>
       </c>
-      <c r="F26" t="str" xml:space="preserve">
+      <c r="F26" t="str">
+        <v>Website redesign idea for Duc Tien Cash &amp; Carry</v>
+      </c>
+      <c r="G26" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Duc Tien Cash &amp; Carry team,
 I came across your website while researching established London businesses that could benefit from a stronger online first impression.
 Your Vietnamese cash and carry / wholesale retail are clear business strengths. However, I noticed that the website times out in preview and uses older page structures, which can make product range, opening hours and directions harder for trade customers to access. That can make potential customers hesitate or leave before contacting you.
@@ -2282,13 +2515,16 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G26" t="str">
-        <v>Sent</v>
-      </c>
       <c r="H26" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="I26" t="str" xml:space="preserve">
+        <v>Sent</v>
+      </c>
+      <c r="I26" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Following up - Website redesign idea for Duc Tien Cash &amp; Carry</v>
+      </c>
+      <c r="K26" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Duc Tien Cash &amp; Carry team,
 Just following up on my previous message about the homepage redesign idea for your website.
 The main opportunity I noticed is that the website times out in preview and uses older page structures, which can make product range, opening hours and directions harder for trade customers to access. A cleaner homepage could help visitors understand your Vietnamese cash and carry / wholesale retail faster and make it easier for them to enquire.
@@ -2300,13 +2536,16 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J26" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="M26" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="L26" t="str" xml:space="preserve">
+      <c r="N26" t="str">
+        <v>Final follow-up - Website redesign idea for Duc Tien Cash &amp; Carry</v>
+      </c>
+      <c r="O26" t="str" xml:space="preserve">
         <v xml:space="preserve">Hi Duc Tien Cash &amp; Carry team,
 I wanted to send one final follow-up in case the website redesign idea is useful for you later.
 My suggestion would be to focus first on a modern mobile-friendly homepage, clearer service sections, stronger trust/project proof and a simpler enquiry path.
@@ -2318,26 +2557,26 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M26" t="str">
-        <v>Sent</v>
-      </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="Q26" t="str">
         <v>2026-09-07</v>
       </c>
-      <c r="O26" t="str">
+      <c r="R26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R26"/>
   </ignoredErrors>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="G2:G1000 J2:J1000 M2:M1000">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
       <formula1>"Draft,Sent,Replied,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O1000">
-      <formula1>"Win,Closed"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
+      <formula1>"Win,Lost"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/excel/Batch_01_Leads_Tracker.xlsx
+++ b/excel/Batch_01_Leads_Tracker.xlsx
@@ -418,8 +418,6 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="32.83203125" customWidth="1"/>
-    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/excel/Batch_01_Leads_Tracker.xlsx
+++ b/excel/Batch_01_Leads_Tracker.xlsx
@@ -2571,7 +2571,7 @@
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
-      <formula1>"Draft,Sent,Replied,Closed"</formula1>
+      <formula1>"Draft,Sent,Replied,Mail Not Found,Bounce Back,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>

--- a/excel/Batch_01_Leads_Tracker.xlsx
+++ b/excel/Batch_01_Leads_Tracker.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="200" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -657,7 +657,7 @@
         <v>Landline: 0208 629 1723; Mobile: 07443 773 773</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">WhatsApp: https://wa.me/447443773773
+        <v xml:space="preserve">[x] WhatsApp: https://wa.me/447443773773
 Checkatrade: https://www.checkatrade.com/trades/yourchoicelocksandglazing
 Contact page: https://yourchoicelocksmiths.co.uk/your_choice_locksmiths_service_contact_us</v>
       </c>
